--- a/data/trans_camb/IP1007-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Clase-trans_camb.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-3,05; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 0,0</t>
+          <t>-1,32; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,52</t>
+          <t>-0,52; 1,25</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,12</t>
+          <t>0,0; 3,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,0</t>
+          <t>-4,08; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 0,0</t>
+          <t>-1,86; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,0</t>
+          <t>-1,81; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,0</t>
+          <t>-0,6; 2,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,0</t>
+          <t>-1,04; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,07</t>
+          <t>-0,3; 0,92</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,8</t>
+          <t>-1,19; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,0</t>
+          <t>-3,59; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 0,91</t>
+          <t>-3,38; 0,58</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,32</t>
+          <t>-2,86; 1,33</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,82</t>
+          <t>-1,56; 0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 0,58</t>
+          <t>-1,8; 0,54</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 0,0</t>
+          <t>-3,97; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,0</t>
+          <t>-4,52; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-2,46; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-2,37; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,39</t>
+          <t>-0,48; 0,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,42</t>
+          <t>-0,47; 0,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,0</t>
+          <t>-0,87; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,34</t>
+          <t>-0,69; 0,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,11</t>
+          <t>-0,5; 0,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,26</t>
+          <t>-0,4; 0,25</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 365,81</t>
+          <t>-100,0; 338,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 137,71</t>
+          <t>-100,0; 121,22</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-87,92; 227,98</t>
+          <t>-84,42; 248,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Clase-trans_camb.xlsx
@@ -631,12 +631,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,0</t>
+          <t>-3,03; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -646,17 +646,17 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 2,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,0</t>
+          <t>-1,56; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,25</t>
+          <t>-0,52; 1,27</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,22 +797,22 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 0,0</t>
+          <t>-3,72; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 0,0</t>
+          <t>-3,44; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 0,6</t>
+          <t>-1,31; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 0,0</t>
+          <t>-1,99; 0,0</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,0</t>
+          <t>-1,5; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,06</t>
+          <t>-0,6; 2,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,0</t>
+          <t>-0,74; 0,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,92</t>
+          <t>-0,3; 1,33</t>
         </is>
       </c>
     </row>
@@ -1260,27 +1260,27 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 0,0</t>
+          <t>-3,87; 0,0</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 0,58</t>
+          <t>-2,88; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,33</t>
+          <t>-2,78; 1,62</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,84</t>
+          <t>-1,81; 0,72</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 0,54</t>
+          <t>-1,88; 0,59</t>
         </is>
       </c>
     </row>
@@ -1421,22 +1421,22 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 0,0</t>
+          <t>-5,16; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,0</t>
+          <t>-6,02; 0,0</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 0,0</t>
+          <t>-3,03; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,0</t>
+          <t>-2,91; 0,0</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,43</t>
+          <t>-0,48; 0,36</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 0,44</t>
+          <t>-0,54; 0,42</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 0,0</t>
+          <t>-0,89; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,34</t>
+          <t>-0,7; 0,27</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,1</t>
+          <t>-0,49; 0,12</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,25</t>
+          <t>-0,43; 0,26</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 338,08</t>
+          <t>-100,0; 293,19</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 121,22</t>
+          <t>-91,06; 152,59</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-84,42; 248,67</t>
+          <t>-86,32; 266,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1007-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP1007-Clase-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-0,5</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>-0,5</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,0</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,56; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>-2,77; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 0,0</t>
+          <t>-1,48; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 1,27</t>
+          <t>-0,52; 1,52</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,75</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,61</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,75</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>-3,76; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-3,74; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,0</t>
+          <t>0,0; 3,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,61</t>
+          <t>-1,47; 0,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,0</t>
+          <t>-2,08; 0,0</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>-0,3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,22</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,22 +1099,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 2,07</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,8; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,6; 2,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,33</t>
+          <t>-0,3; 1,07</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>74,68%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,63</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,01</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>-0,59</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,63</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 1,82</t>
+          <t>-2,85; 0,91</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,0</t>
+          <t>-2,38; 1,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 0,93</t>
+          <t>-1,2; 1,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 1,62</t>
+          <t>-3,38; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 0,72</t>
+          <t>-1,81; 0,82</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,59</t>
+          <t>-1,83; 0,58</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-56,12%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-21,28%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>1,42%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-56,12%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-21,28%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1373,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-0,89</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,83; 0,0</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-4,47; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
     </row>
@@ -1449,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-0,3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-0,05</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>-0,1</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,3</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-0,12</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,36</t>
+          <t>-0,89; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 0,42</t>
+          <t>-0,68; 0,34</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 0,0</t>
+          <t>-0,49; 0,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 0,27</t>
+          <t>-0,5; 0,42</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 0,12</t>
+          <t>-0,51; 0,11</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 0,26</t>
+          <t>-0,46; 0,26</t>
         </is>
       </c>
     </row>
@@ -1605,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-75,71%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-30,6%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-20,2%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>-36,31%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-75,71%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-30,6%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 365,81</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 293,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-91,06; 152,59</t>
+          <t>-100,0; 137,71</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 266,15</t>
+          <t>-87,92; 227,98</t>
         </is>
       </c>
     </row>
